--- a/portfolio-data.xlsx
+++ b/portfolio-data.xlsx
@@ -927,7 +927,7 @@
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/Iamsaudkhan</t>
+          <t>https://github.com/MOHDSAUD888</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
